--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/MAINE_2017.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/MAINE_2017.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C10">
